--- a/output/IL_VANTO.xlsx
+++ b/output/IL_VANTO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hookah - 50 ML</t>
+          <t>Blue Essence - 50 ML</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smoking Hot – Kilian</t>
+          <t>Dylan Blue - Versace</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -466,12 +466,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gourmand Café - 50 ML</t>
+          <t>Carnation - 50 ML</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Giardini di Toscana – Bianco Latte</t>
+          <t>Aventus - Creed</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -486,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ethereal Cognac - 50 ML</t>
+          <t>Chillwave - 50 ML</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Angel's Share – Kilian</t>
+          <t>Pacific Chill – Louis Vuitton</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -506,12 +506,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sweet Chestnut - 50 ML</t>
+          <t>Citranova - 50 ML</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Emporio Armani – SWY Intensely</t>
+          <t>Y Eau de Parfum — YSL</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -546,12 +546,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Obsidian - 50 ML</t>
+          <t>Espionage - 50 ML</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Symphony – Louis Vuitton</t>
+          <t>Naxos – Xerjoff</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -566,12 +566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Euphoria - 50 ML</t>
+          <t>Ethereal Cognac - 50 ML</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Imagination – Louis Vuitton</t>
+          <t>Angel's Share – Kilian</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -586,12 +586,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chillwave - 50 ML</t>
+          <t>Euphoria - 50 ML</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pacific Chill – Louis Vuitton</t>
+          <t>Imagination – Louis Vuitton</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -606,12 +606,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fruity Jungle - 50 ML</t>
+          <t>Feral Rose - 50 ML</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Le Beau Le Parfum – Jean Paul Gaultier</t>
+          <t>Oud Satin Mood – MFK</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -626,12 +626,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fruity Musk - 50 ML</t>
+          <t>Fruity Jungle - 50 ML</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Erba Pura – Xerjoff</t>
+          <t>Le Beau Le Parfum – Jean Paul Gaultier</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -646,12 +646,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tropica Xtreme - 50 ML</t>
+          <t>Fruity Musk - 50 ML</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>God Of Fire - Stèphane Humbert</t>
+          <t>Erba Pura – Xerjoff</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -666,12 +666,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Feral Rose - 50 ML</t>
+          <t>Golden Essence - 50 ML</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oud Satin Mood – MFK</t>
+          <t>Le Male Elixir – jean paul gaultier</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Golden Essence - 50 ML</t>
+          <t>Gourmand Café - 50 ML</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Le Male Elixir – jean paul gaultier</t>
+          <t>Giardini di Toscana – Bianco Latte</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -726,12 +726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carnation - 50 ML</t>
+          <t>Hookah - 50 ML</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aventus - Creed</t>
+          <t>Smoking Hot – Kilian</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -746,12 +746,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oud Exotica - 50 ML</t>
+          <t>Iced Bergamot - 50 ML</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oud Maracujá – Maison Crivelli</t>
+          <t>MYSLF – YSL</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -766,12 +766,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Velvet Dream - 50 ML</t>
+          <t>Midnight Oman - 50 ML</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Born in Roma Intense – Valentino</t>
+          <t>Oud Isphahan – Dior</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Espionage - 50 ML</t>
+          <t>Obsidian - 50 ML</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Naxos – Xerjoff</t>
+          <t>Symphony – Louis Vuitton</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -806,12 +806,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Royal Hibiscus - 50 ML</t>
+          <t>Oud Exotica - 50 ML</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maison Crivelli – Hibiscus Mahjad</t>
+          <t>Oud Maracujá – Maison Crivelli</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -846,12 +846,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Midnight Oman - 50 ML</t>
+          <t>Royal Hibiscus - 50 ML</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oud Isphahan – Dior</t>
+          <t>Maison Crivelli – Hibiscus Mahjad</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -866,12 +866,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Iced Bergamot - 50 ML</t>
+          <t>Saffron Rum - 50 ML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MYSLF – YSL</t>
+          <t>Angels' Share Paradis – Kilian</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citranova - 50 ML</t>
+          <t>Seaside Colada - 50 ML</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Y Eau de Parfum — YSL</t>
+          <t>Le Beau Paradise Garden - JPG</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -926,12 +926,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Essence - 50 ML</t>
+          <t>Sweet Chestnut - 50 ML</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dylan Blue - Versace</t>
+          <t>Emporio Armani – SWY Intensely</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seaside Colada - 50 ML</t>
+          <t>Tropica Xtreme - 50 ML</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Le Beau Paradise Garden - JPG</t>
+          <t>God Of Fire - Stèphane Humbert</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -966,12 +966,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saffron Rum - 50 ML</t>
+          <t>Velvet Dream - 50 ML</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Angels' Share Paradis – Kilian</t>
+          <t>Born in Roma Intense – Valentino</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Minerva - 50 ML</t>
+          <t>Baked Vanilla - 50 ML</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vanilla Skin – Phlur</t>
+          <t>Vanilla 28 – Kayali</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wild Berry - 50 ML</t>
+          <t>CLOUD9 - 50 ML</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Strawberry Letter – Phlur</t>
+          <t>Her – Burberry</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLOUD9 - 50 ML</t>
+          <t>Desire - 50 ML</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Her – Burberry</t>
+          <t>Libre – YSL</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VAL - 50 ML</t>
+          <t>Devil's Lychee - 50 ML</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valentino Donna - Valentino</t>
+          <t>Delina – Parfums de Marly</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Devil's Lychee - 50 ML</t>
+          <t>Ethereal Cognac - 50 ML</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Delina – Parfums de Marly</t>
+          <t>Angel's Share – Kilian</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SINFUL ROSE - 50 ML</t>
+          <t>Feral Rose - 50 ML</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Roses Vanille – Mancera</t>
+          <t>Oud Satin Mood – MFK</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Desire - 50 ML</t>
+          <t>Fruity Musk - 50 ML</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Libre – YSL</t>
+          <t>Erba Pura – Xerjoff</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Baked Vanilla - 50 ML</t>
+          <t>Gourmand Café - 50 ML</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vanilla 28 – Kayali</t>
+          <t>Giardini di Toscana – Bianco Latte</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1166,15 +1166,175 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Midnight Oman - 50 ML</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oud Isphahan – Dior</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Minerva - 50 ML</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vanilla Skin – Phlur</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Nude Bloom - 50 ML</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>PARADOX – PRADA</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D40" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Obsidian - 50 ML</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Symphony – Louis Vuitton</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Royal Hibiscus - 50 ML</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Maison Crivelli – Hibiscus Mahjad</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SINFUL ROSE - 50 ML</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Roses Vanille – Mancera</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Saffron Rum - 50 ML</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Angels' Share Paradis – Kilian</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VAL - 50 ML</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Valentino Donna - Valentino</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wild Berry - 50 ML</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Strawberry Letter – Phlur</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>899</v>
       </c>
     </row>
